--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124295214</v>
+        <v>124294849</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461495</v>
+        <v>461329</v>
       </c>
       <c r="R2" t="n">
-        <v>7050108</v>
+        <v>7050171</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,17 +790,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124294849</v>
+        <v>124295214</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,42 +813,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461329</v>
+        <v>461495</v>
       </c>
       <c r="R3" t="n">
-        <v>7050171</v>
+        <v>7050108</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124469127</v>
+        <v>124468338</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,43 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461609</v>
+        <v>461500</v>
       </c>
       <c r="R5" t="n">
-        <v>7050050</v>
+        <v>7050112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468176</v>
+        <v>124468866</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461418</v>
+        <v>461582</v>
       </c>
       <c r="R6" t="n">
-        <v>7050112</v>
+        <v>7050058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,12 +1253,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1391,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468946</v>
+        <v>124468687</v>
       </c>
       <c r="B8" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,34 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461594</v>
+        <v>461555</v>
       </c>
       <c r="R8" t="n">
-        <v>7050052</v>
+        <v>7050078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,12 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,19 +1487,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468902</v>
+        <v>124469540</v>
       </c>
       <c r="B9" t="n">
         <v>77743</v>
@@ -1544,14 +1535,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461582</v>
+        <v>461502</v>
       </c>
       <c r="R9" t="n">
-        <v>7050071</v>
+        <v>7050054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,22 +1604,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468318</v>
+        <v>124468902</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461483</v>
+        <v>461582</v>
       </c>
       <c r="R10" t="n">
-        <v>7050111</v>
+        <v>7050071</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1701,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468954</v>
+        <v>124468605</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,37 +1749,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461595</v>
+        <v>461539</v>
       </c>
       <c r="R11" t="n">
-        <v>7050056</v>
+        <v>7050084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1818,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,7 +1832,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1863,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468687</v>
+        <v>124468946</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,34 +1866,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461555</v>
+        <v>461594</v>
       </c>
       <c r="R12" t="n">
-        <v>7050078</v>
+        <v>7050052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,12 +1935,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,22 +1955,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469219</v>
+        <v>124468263</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,43 +1983,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461680</v>
+        <v>461459</v>
       </c>
       <c r="R13" t="n">
-        <v>7049995</v>
+        <v>7050134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2074,12 +2052,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,19 +2072,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124469540</v>
+        <v>124469194</v>
       </c>
       <c r="B14" t="n">
         <v>77743</v>
@@ -2142,14 +2120,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461502</v>
+        <v>461630</v>
       </c>
       <c r="R14" t="n">
-        <v>7050054</v>
+        <v>7050036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2181,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2191,12 +2169,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,12 +2189,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2340,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468605</v>
+        <v>124468898</v>
       </c>
       <c r="B16" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2356,34 +2334,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461539</v>
+        <v>461593</v>
       </c>
       <c r="R16" t="n">
-        <v>7050084</v>
+        <v>7050052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2425,12 +2403,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,22 +2423,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124469194</v>
+        <v>124468954</v>
       </c>
       <c r="B17" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,34 +2451,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461630</v>
+        <v>461595</v>
       </c>
       <c r="R17" t="n">
-        <v>7050036</v>
+        <v>7050056</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,7 +2528,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,6 +2537,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2574,7 +2556,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468866</v>
+        <v>124468401</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2614,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461582</v>
+        <v>461503</v>
       </c>
       <c r="R18" t="n">
-        <v>7050058</v>
+        <v>7050083</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2631,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2659,12 +2641,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,17 +2666,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468401</v>
+        <v>124468367</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,34 +2689,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461503</v>
+        <v>461494</v>
       </c>
       <c r="R19" t="n">
-        <v>7050083</v>
+        <v>7050108</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,7 +2748,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2776,12 +2758,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,22 +2778,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468898</v>
+        <v>124468318</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,34 +2806,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461593</v>
+        <v>461483</v>
       </c>
       <c r="R20" t="n">
-        <v>7050052</v>
+        <v>7050111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2883,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2893,12 +2875,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,22 +2895,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468367</v>
+        <v>124469282</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,21 +2923,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2965,10 +2947,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461494</v>
+        <v>461663</v>
       </c>
       <c r="R21" t="n">
-        <v>7050108</v>
+        <v>7050034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3000,7 +2982,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,12 +2992,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3042,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468338</v>
+        <v>124469127</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3058,34 +3035,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461500</v>
+        <v>461609</v>
       </c>
       <c r="R22" t="n">
-        <v>7050112</v>
+        <v>7050050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3117,7 +3103,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3127,12 +3113,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3159,10 +3145,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124469282</v>
+        <v>124469219</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3175,34 +3161,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461663</v>
+        <v>461680</v>
       </c>
       <c r="R23" t="n">
-        <v>7050034</v>
+        <v>7049995</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3244,7 +3239,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,19 +3259,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124468263</v>
+        <v>124468176</v>
       </c>
       <c r="B24" t="n">
         <v>74901</v>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461459</v>
+        <v>461418</v>
       </c>
       <c r="R24" t="n">
-        <v>7050134</v>
+        <v>7050112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124294849</v>
+        <v>124295214</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461329</v>
+        <v>461495</v>
       </c>
       <c r="R2" t="n">
-        <v>7050171</v>
+        <v>7050108</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,14 +785,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124295214</v>
+        <v>124295359</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461495</v>
+        <v>461531</v>
       </c>
       <c r="R3" t="n">
-        <v>7050108</v>
+        <v>7050055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124295359</v>
+        <v>124294849</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,37 +925,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461531</v>
+        <v>461329</v>
       </c>
       <c r="R4" t="n">
-        <v>7050055</v>
+        <v>7050171</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,14 +1024,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468338</v>
+        <v>124468263</v>
       </c>
       <c r="B5" t="n">
         <v>74901</v>
@@ -1067,14 +1067,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461500</v>
+        <v>461459</v>
       </c>
       <c r="R5" t="n">
-        <v>7050112</v>
+        <v>7050134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468866</v>
+        <v>124468176</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461582</v>
+        <v>461418</v>
       </c>
       <c r="R6" t="n">
-        <v>7050058</v>
+        <v>7050112</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468512</v>
+        <v>124468946</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>88359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,41 +1277,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461530</v>
+        <v>461594</v>
       </c>
       <c r="R7" t="n">
-        <v>7050097</v>
+        <v>7050052</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,22 +1370,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468687</v>
+        <v>124468338</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,34 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461555</v>
+        <v>461500</v>
       </c>
       <c r="R8" t="n">
-        <v>7050078</v>
+        <v>7050112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,19 +1487,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124469540</v>
+        <v>124468605</v>
       </c>
       <c r="B9" t="n">
         <v>77743</v>
@@ -1535,14 +1535,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461502</v>
+        <v>461539</v>
       </c>
       <c r="R9" t="n">
-        <v>7050054</v>
+        <v>7050084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,22 +1604,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468902</v>
+        <v>124468367</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461582</v>
+        <v>461494</v>
       </c>
       <c r="R10" t="n">
-        <v>7050071</v>
+        <v>7050108</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468605</v>
+        <v>124468512</v>
       </c>
       <c r="B11" t="n">
-        <v>77743</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,41 +1745,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461539</v>
+        <v>461530</v>
       </c>
       <c r="R11" t="n">
-        <v>7050084</v>
+        <v>7050097</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468946</v>
+        <v>124468318</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,34 +1866,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461594</v>
+        <v>461483</v>
       </c>
       <c r="R12" t="n">
-        <v>7050052</v>
+        <v>7050111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,22 +1955,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468263</v>
+        <v>124469540</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461459</v>
+        <v>461502</v>
       </c>
       <c r="R13" t="n">
-        <v>7050134</v>
+        <v>7050054</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,12 +2072,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468413</v>
+        <v>124468954</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,34 +2217,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461514</v>
+        <v>461595</v>
       </c>
       <c r="R15" t="n">
-        <v>7050104</v>
+        <v>7050056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2279,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,12 +2289,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,6 +2303,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2318,10 +2322,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468898</v>
+        <v>124469127</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,34 +2338,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461593</v>
+        <v>461609</v>
       </c>
       <c r="R16" t="n">
-        <v>7050052</v>
+        <v>7050050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,12 +2416,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,17 +2441,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468954</v>
+        <v>124468687</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,37 +2464,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461595</v>
+        <v>461555</v>
       </c>
       <c r="R17" t="n">
-        <v>7050056</v>
+        <v>7050078</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,7 +2523,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2523,12 +2533,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,7 +2547,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2556,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468401</v>
+        <v>124468898</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,21 +2581,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2596,10 +2605,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461503</v>
+        <v>461593</v>
       </c>
       <c r="R18" t="n">
-        <v>7050083</v>
+        <v>7050052</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2641,12 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468367</v>
+        <v>124468401</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2689,34 +2698,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461494</v>
+        <v>461503</v>
       </c>
       <c r="R19" t="n">
-        <v>7050108</v>
+        <v>7050083</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2748,7 +2757,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2758,12 +2767,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2778,19 +2787,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468318</v>
+        <v>124468866</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2826,14 +2835,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461483</v>
+        <v>461582</v>
       </c>
       <c r="R20" t="n">
-        <v>7050111</v>
+        <v>7050058</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2865,7 +2874,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,12 +2884,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,22 +2904,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124469282</v>
+        <v>124468413</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,21 +2932,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2947,10 +2956,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461663</v>
+        <v>461514</v>
       </c>
       <c r="R21" t="n">
-        <v>7050034</v>
+        <v>7050104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2982,7 +2991,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2992,7 +3001,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124469127</v>
+        <v>124468902</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,43 +3049,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461609</v>
+        <v>461582</v>
       </c>
       <c r="R22" t="n">
-        <v>7050050</v>
+        <v>7050071</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3103,7 +3108,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3113,12 +3118,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,12 +3138,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3271,10 +3276,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124468176</v>
+        <v>124469282</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3287,21 +3292,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,10 +3316,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461418</v>
+        <v>461663</v>
       </c>
       <c r="R24" t="n">
-        <v>7050112</v>
+        <v>7050034</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3356,12 +3361,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124295214</v>
+        <v>124295359</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461495</v>
+        <v>461531</v>
       </c>
       <c r="R2" t="n">
-        <v>7050108</v>
+        <v>7050055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124295359</v>
+        <v>124294849</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461531</v>
+        <v>461329</v>
       </c>
       <c r="R3" t="n">
-        <v>7050055</v>
+        <v>7050171</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,17 +907,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124294849</v>
+        <v>124295214</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,42 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461329</v>
+        <v>461495</v>
       </c>
       <c r="R4" t="n">
-        <v>7050171</v>
+        <v>7050108</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,14 +1024,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468263</v>
+        <v>124468367</v>
       </c>
       <c r="B5" t="n">
         <v>74901</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461459</v>
+        <v>461494</v>
       </c>
       <c r="R5" t="n">
-        <v>7050134</v>
+        <v>7050108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468176</v>
+        <v>124469282</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461418</v>
+        <v>461663</v>
       </c>
       <c r="R6" t="n">
-        <v>7050112</v>
+        <v>7050034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468946</v>
+        <v>124468512</v>
       </c>
       <c r="B7" t="n">
-        <v>88359</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,41 +1272,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461594</v>
+        <v>461530</v>
       </c>
       <c r="R7" t="n">
-        <v>7050052</v>
+        <v>7050097</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468338</v>
+        <v>124469194</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,34 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461500</v>
+        <v>461630</v>
       </c>
       <c r="R8" t="n">
-        <v>7050112</v>
+        <v>7050036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,19 +1482,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468605</v>
+        <v>124468902</v>
       </c>
       <c r="B9" t="n">
         <v>77743</v>
@@ -1539,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461539</v>
+        <v>461582</v>
       </c>
       <c r="R9" t="n">
-        <v>7050084</v>
+        <v>7050071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1616,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468367</v>
+        <v>124468687</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461494</v>
+        <v>461555</v>
       </c>
       <c r="R10" t="n">
-        <v>7050108</v>
+        <v>7050078</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,12 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468512</v>
+        <v>124468954</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,41 +1740,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461530</v>
+        <v>461595</v>
       </c>
       <c r="R11" t="n">
-        <v>7050097</v>
+        <v>7050056</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,12 +1816,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,6 +1830,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1850,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468318</v>
+        <v>124468898</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,34 +1865,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461483</v>
+        <v>461593</v>
       </c>
       <c r="R12" t="n">
-        <v>7050111</v>
+        <v>7050052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,12 +1934,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,22 +1954,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469540</v>
+        <v>124469219</v>
       </c>
       <c r="B13" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,34 +1982,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461502</v>
+        <v>461680</v>
       </c>
       <c r="R13" t="n">
-        <v>7050054</v>
+        <v>7049995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,17 +2085,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124469194</v>
+        <v>124468866</v>
       </c>
       <c r="B14" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,34 +2108,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461630</v>
+        <v>461582</v>
       </c>
       <c r="R14" t="n">
-        <v>7050036</v>
+        <v>7050058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,12 +2177,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,22 +2197,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468954</v>
+        <v>124468413</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,37 +2225,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461595</v>
+        <v>461514</v>
       </c>
       <c r="R15" t="n">
-        <v>7050056</v>
+        <v>7050104</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,12 +2294,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2308,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2322,7 +2326,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124469127</v>
+        <v>124468318</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2355,26 +2359,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461609</v>
+        <v>461483</v>
       </c>
       <c r="R16" t="n">
-        <v>7050050</v>
+        <v>7050111</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2416,12 +2411,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,22 +2431,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468687</v>
+        <v>124468176</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,21 +2459,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2488,10 +2483,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461555</v>
+        <v>461418</v>
       </c>
       <c r="R17" t="n">
-        <v>7050078</v>
+        <v>7050112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,7 +2518,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2533,12 +2528,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468898</v>
+        <v>124469127</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,34 +2576,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461593</v>
+        <v>461609</v>
       </c>
       <c r="R18" t="n">
-        <v>7050052</v>
+        <v>7050050</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,7 +2644,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,12 +2654,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2799,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468866</v>
+        <v>124468946</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2819,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461582</v>
+        <v>461594</v>
       </c>
       <c r="R20" t="n">
-        <v>7050058</v>
+        <v>7050052</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2874,7 +2878,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2884,12 +2888,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2920,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468413</v>
+        <v>124469540</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,34 +2936,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461514</v>
+        <v>461502</v>
       </c>
       <c r="R21" t="n">
-        <v>7050104</v>
+        <v>7050054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3001,12 +3005,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,22 +3025,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468902</v>
+        <v>124468263</v>
       </c>
       <c r="B22" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,21 +3053,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +3077,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461582</v>
+        <v>461459</v>
       </c>
       <c r="R22" t="n">
-        <v>7050071</v>
+        <v>7050134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3108,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3118,7 +3122,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3150,10 +3154,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124469219</v>
+        <v>124468605</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,43 +3170,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461680</v>
+        <v>461539</v>
       </c>
       <c r="R23" t="n">
-        <v>7049995</v>
+        <v>7050084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3244,12 +3239,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,22 +3259,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124469282</v>
+        <v>124468338</v>
       </c>
       <c r="B24" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3292,34 +3287,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461663</v>
+        <v>461500</v>
       </c>
       <c r="R24" t="n">
-        <v>7050034</v>
+        <v>7050112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3351,7 +3346,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3361,7 +3356,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,12 +3376,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124295359</v>
+        <v>124295214</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461531</v>
+        <v>461495</v>
       </c>
       <c r="R2" t="n">
-        <v>7050055</v>
+        <v>7050108</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124294849</v>
+        <v>124295359</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461329</v>
+        <v>461531</v>
       </c>
       <c r="R3" t="n">
-        <v>7050171</v>
+        <v>7050055</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124295214</v>
+        <v>124294849</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,37 +925,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461495</v>
+        <v>461329</v>
       </c>
       <c r="R4" t="n">
-        <v>7050108</v>
+        <v>7050171</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468367</v>
+        <v>124468512</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,41 +1043,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461494</v>
+        <v>461530</v>
       </c>
       <c r="R5" t="n">
-        <v>7050108</v>
+        <v>7050097</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468512</v>
+        <v>124469540</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,41 +1272,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461530</v>
+        <v>461502</v>
       </c>
       <c r="R7" t="n">
-        <v>7050097</v>
+        <v>7050054</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124469194</v>
+        <v>124469219</v>
       </c>
       <c r="B8" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,34 +1393,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461630</v>
+        <v>461680</v>
       </c>
       <c r="R8" t="n">
-        <v>7050036</v>
+        <v>7049995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,19 +1491,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468902</v>
+        <v>124469194</v>
       </c>
       <c r="B9" t="n">
         <v>77743</v>
@@ -1534,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461582</v>
+        <v>461630</v>
       </c>
       <c r="R9" t="n">
-        <v>7050071</v>
+        <v>7050036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468687</v>
+        <v>124468946</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,34 +1636,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461555</v>
+        <v>461594</v>
       </c>
       <c r="R10" t="n">
-        <v>7050078</v>
+        <v>7050052</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,22 +1725,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468954</v>
+        <v>124468866</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,37 +1753,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461595</v>
+        <v>461582</v>
       </c>
       <c r="R11" t="n">
-        <v>7050056</v>
+        <v>7050058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,12 +1822,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,19 +1836,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1966,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469219</v>
+        <v>124468605</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,43 +1987,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461680</v>
+        <v>461539</v>
       </c>
       <c r="R13" t="n">
-        <v>7049995</v>
+        <v>7050084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,12 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,19 +2076,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468866</v>
+        <v>124468687</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2128,14 +2124,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461582</v>
+        <v>461555</v>
       </c>
       <c r="R14" t="n">
-        <v>7050058</v>
+        <v>7050078</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,12 +2173,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,19 +2193,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468413</v>
+        <v>124469127</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2242,17 +2238,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461514</v>
+        <v>461609</v>
       </c>
       <c r="R15" t="n">
-        <v>7050104</v>
+        <v>7050050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2289,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2299,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,22 +2319,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468318</v>
+        <v>124468367</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,21 +2347,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461483</v>
+        <v>461494</v>
       </c>
       <c r="R16" t="n">
-        <v>7050111</v>
+        <v>7050108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2411,12 +2416,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468176</v>
+        <v>124468902</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2459,21 +2464,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2483,10 +2488,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461418</v>
+        <v>461582</v>
       </c>
       <c r="R17" t="n">
-        <v>7050112</v>
+        <v>7050071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,7 +2523,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2528,12 +2533,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,7 +2565,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124469127</v>
+        <v>124468413</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2593,26 +2598,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461609</v>
+        <v>461514</v>
       </c>
       <c r="R18" t="n">
-        <v>7050050</v>
+        <v>7050104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,7 +2640,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,12 +2650,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,22 +2670,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468401</v>
+        <v>124468263</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,34 +2698,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461503</v>
+        <v>461459</v>
       </c>
       <c r="R19" t="n">
-        <v>7050083</v>
+        <v>7050134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,7 +2757,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2771,12 +2767,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,22 +2787,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468946</v>
+        <v>124468401</v>
       </c>
       <c r="B20" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2819,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461594</v>
+        <v>461503</v>
       </c>
       <c r="R20" t="n">
-        <v>7050052</v>
+        <v>7050083</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,7 +2874,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2888,12 +2884,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2920,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124469540</v>
+        <v>124468338</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2936,21 +2932,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,10 +2956,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461502</v>
+        <v>461500</v>
       </c>
       <c r="R21" t="n">
-        <v>7050054</v>
+        <v>7050112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2995,7 +2991,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +3001,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3030,17 +3026,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468263</v>
+        <v>124468954</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,34 +3049,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461459</v>
+        <v>461595</v>
       </c>
       <c r="R22" t="n">
-        <v>7050134</v>
+        <v>7050056</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +3111,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,12 +3121,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,6 +3135,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468605</v>
+        <v>124468176</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461539</v>
+        <v>461418</v>
       </c>
       <c r="R23" t="n">
-        <v>7050084</v>
+        <v>7050112</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124468338</v>
+        <v>124468318</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461500</v>
+        <v>461483</v>
       </c>
       <c r="R24" t="n">
-        <v>7050112</v>
+        <v>7050111</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,12 +3376,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -1503,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124469194</v>
+        <v>124468946</v>
       </c>
       <c r="B9" t="n">
-        <v>77743</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461630</v>
+        <v>461594</v>
       </c>
       <c r="R9" t="n">
-        <v>7050036</v>
+        <v>7050052</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468946</v>
+        <v>124469194</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>77743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,34 +1636,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461594</v>
+        <v>461630</v>
       </c>
       <c r="R10" t="n">
-        <v>7050052</v>
+        <v>7050036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,12 +1725,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468338</v>
+        <v>124468954</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,34 +2932,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461500</v>
+        <v>461595</v>
       </c>
       <c r="R21" t="n">
-        <v>7050112</v>
+        <v>7050056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3001,12 +3004,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3015,28 +3018,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468954</v>
+        <v>124468338</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,37 +3053,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461595</v>
+        <v>461500</v>
       </c>
       <c r="R22" t="n">
-        <v>7050056</v>
+        <v>7050112</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3111,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3121,12 +3122,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,19 +3136,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124295214</v>
+        <v>124294849</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461495</v>
+        <v>461329</v>
       </c>
       <c r="R2" t="n">
-        <v>7050108</v>
+        <v>7050171</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124294849</v>
+        <v>124295214</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,42 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461329</v>
+        <v>461495</v>
       </c>
       <c r="R4" t="n">
-        <v>7050171</v>
+        <v>7050108</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468512</v>
+        <v>124468946</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,41 +1043,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461530</v>
+        <v>461594</v>
       </c>
       <c r="R5" t="n">
-        <v>7050097</v>
+        <v>7050052</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,19 +1136,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124469282</v>
+        <v>124469540</v>
       </c>
       <c r="B6" t="n">
         <v>77743</v>
@@ -1184,14 +1184,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461663</v>
+        <v>461502</v>
       </c>
       <c r="R6" t="n">
-        <v>7050034</v>
+        <v>7050054</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124469540</v>
+        <v>124468866</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461502</v>
+        <v>461582</v>
       </c>
       <c r="R7" t="n">
-        <v>7050054</v>
+        <v>7050058</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124469219</v>
+        <v>124468902</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,43 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461680</v>
+        <v>461582</v>
       </c>
       <c r="R8" t="n">
-        <v>7049995</v>
+        <v>7050071</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468946</v>
+        <v>124468512</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,41 +1511,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461594</v>
+        <v>461530</v>
       </c>
       <c r="R9" t="n">
-        <v>7050052</v>
+        <v>7050097</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1604,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124469194</v>
+        <v>124469219</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,34 +1632,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461630</v>
+        <v>461680</v>
       </c>
       <c r="R10" t="n">
-        <v>7050036</v>
+        <v>7049995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,12 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,22 +1730,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468866</v>
+        <v>124468367</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,34 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461582</v>
+        <v>461494</v>
       </c>
       <c r="R11" t="n">
-        <v>7050058</v>
+        <v>7050108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,12 +1827,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,22 +1847,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468898</v>
+        <v>124468318</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,34 +1875,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461593</v>
+        <v>461483</v>
       </c>
       <c r="R12" t="n">
-        <v>7050052</v>
+        <v>7050111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1944,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,22 +1964,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468605</v>
+        <v>124468413</v>
       </c>
       <c r="B13" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,21 +1992,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461539</v>
+        <v>461514</v>
       </c>
       <c r="R13" t="n">
-        <v>7050084</v>
+        <v>7050104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2061,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468687</v>
+        <v>124468263</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,21 +2109,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2128,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461555</v>
+        <v>461459</v>
       </c>
       <c r="R14" t="n">
-        <v>7050078</v>
+        <v>7050134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2173,12 +2178,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124469127</v>
+        <v>124468605</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,43 +2226,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461609</v>
+        <v>461539</v>
       </c>
       <c r="R15" t="n">
-        <v>7050050</v>
+        <v>7050084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,12 +2295,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,22 +2315,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468367</v>
+        <v>124468898</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,34 +2343,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461494</v>
+        <v>461593</v>
       </c>
       <c r="R16" t="n">
-        <v>7050108</v>
+        <v>7050052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,7 +2402,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2416,12 +2412,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,22 +2432,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468902</v>
+        <v>124468687</v>
       </c>
       <c r="B17" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,21 +2460,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2488,10 +2484,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461582</v>
+        <v>461555</v>
       </c>
       <c r="R17" t="n">
-        <v>7050071</v>
+        <v>7050078</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2533,12 +2529,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,10 +2561,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468413</v>
+        <v>124468176</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2605,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461514</v>
+        <v>461418</v>
       </c>
       <c r="R18" t="n">
-        <v>7050104</v>
+        <v>7050112</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,12 +2646,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,7 +2678,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468263</v>
+        <v>124468338</v>
       </c>
       <c r="B19" t="n">
         <v>74901</v>
@@ -2718,14 +2714,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461459</v>
+        <v>461500</v>
       </c>
       <c r="R19" t="n">
-        <v>7050134</v>
+        <v>7050112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2757,7 +2753,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2767,12 +2763,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,22 +2783,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468401</v>
+        <v>124469194</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,34 +2811,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461503</v>
+        <v>461630</v>
       </c>
       <c r="R20" t="n">
-        <v>7050083</v>
+        <v>7050036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2874,7 +2870,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2884,12 +2880,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2904,22 +2900,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468954</v>
+        <v>124468401</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,37 +2928,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461595</v>
+        <v>461503</v>
       </c>
       <c r="R21" t="n">
-        <v>7050056</v>
+        <v>7050083</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +2997,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3018,29 +3011,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468338</v>
+        <v>124469127</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,34 +3045,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461500</v>
+        <v>461609</v>
       </c>
       <c r="R22" t="n">
-        <v>7050112</v>
+        <v>7050050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +3113,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,12 +3123,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3154,10 +3155,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468176</v>
+        <v>124468954</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,34 +3171,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461418</v>
+        <v>461595</v>
       </c>
       <c r="R23" t="n">
-        <v>7050112</v>
+        <v>7050056</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3229,7 +3233,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3239,12 +3243,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3253,6 +3257,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3271,10 +3276,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124468318</v>
+        <v>124469282</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3287,21 +3292,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,10 +3316,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461483</v>
+        <v>461663</v>
       </c>
       <c r="R24" t="n">
-        <v>7050111</v>
+        <v>7050034</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3356,12 +3361,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468866</v>
+        <v>124468512</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,41 +1277,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461582</v>
+        <v>461530</v>
       </c>
       <c r="R7" t="n">
-        <v>7050058</v>
+        <v>7050097</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,12 +1370,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468512</v>
+        <v>124468866</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,41 +1511,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461530</v>
+        <v>461582</v>
       </c>
       <c r="R9" t="n">
-        <v>7050097</v>
+        <v>7050058</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124294849</v>
+        <v>124295214</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461329</v>
+        <v>461495</v>
       </c>
       <c r="R2" t="n">
-        <v>7050171</v>
+        <v>7050108</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124295214</v>
+        <v>124468954</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461495</v>
+        <v>461595</v>
       </c>
       <c r="R4" t="n">
-        <v>7050108</v>
+        <v>7050056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,27 +982,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,28 +1011,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468946</v>
+        <v>124469282</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>77743</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1046,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461594</v>
+        <v>461663</v>
       </c>
       <c r="R5" t="n">
-        <v>7050052</v>
+        <v>7050034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,19 +1130,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124469540</v>
+        <v>124468605</v>
       </c>
       <c r="B6" t="n">
         <v>77743</v>
@@ -1184,14 +1178,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461502</v>
+        <v>461539</v>
       </c>
       <c r="R6" t="n">
-        <v>7050054</v>
+        <v>7050084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468512</v>
+        <v>124468946</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>88359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,41 +1271,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461530</v>
+        <v>461594</v>
       </c>
       <c r="R7" t="n">
-        <v>7050097</v>
+        <v>7050052</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,19 +1364,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468902</v>
+        <v>124469540</v>
       </c>
       <c r="B8" t="n">
         <v>77743</v>
@@ -1418,14 +1412,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461582</v>
+        <v>461502</v>
       </c>
       <c r="R8" t="n">
-        <v>7050071</v>
+        <v>7050054</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468866</v>
+        <v>124468176</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,34 +1509,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461582</v>
+        <v>461418</v>
       </c>
       <c r="R9" t="n">
-        <v>7050058</v>
+        <v>7050112</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,22 +1598,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124469219</v>
+        <v>124468263</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,43 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461680</v>
+        <v>461459</v>
       </c>
       <c r="R10" t="n">
-        <v>7049995</v>
+        <v>7050134</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,22 +1715,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468367</v>
+        <v>124468318</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461494</v>
+        <v>461483</v>
       </c>
       <c r="R11" t="n">
-        <v>7050108</v>
+        <v>7050111</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,12 +1812,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,7 +1844,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468318</v>
+        <v>124468687</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1899,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461483</v>
+        <v>461555</v>
       </c>
       <c r="R12" t="n">
-        <v>7050111</v>
+        <v>7050078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,12 +1929,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,7 +1961,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468413</v>
+        <v>124469127</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2009,17 +1994,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461514</v>
+        <v>461609</v>
       </c>
       <c r="R13" t="n">
-        <v>7050104</v>
+        <v>7050050</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2061,12 +2055,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,22 +2075,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468263</v>
+        <v>124469219</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,34 +2103,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461459</v>
+        <v>461680</v>
       </c>
       <c r="R14" t="n">
-        <v>7050134</v>
+        <v>7049995</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,12 +2181,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,22 +2201,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468605</v>
+        <v>124468866</v>
       </c>
       <c r="B15" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,34 +2229,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461539</v>
+        <v>461582</v>
       </c>
       <c r="R15" t="n">
-        <v>7050084</v>
+        <v>7050058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2295,12 +2298,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2315,22 +2318,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468898</v>
+        <v>124468338</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,21 +2346,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,10 +2370,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461593</v>
+        <v>461500</v>
       </c>
       <c r="R16" t="n">
-        <v>7050052</v>
+        <v>7050112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2402,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2412,12 +2415,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468687</v>
+        <v>124468902</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,21 +2463,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2484,10 +2487,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461555</v>
+        <v>461582</v>
       </c>
       <c r="R17" t="n">
-        <v>7050078</v>
+        <v>7050071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2529,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468176</v>
+        <v>124469194</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,21 +2580,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2604,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461418</v>
+        <v>461630</v>
       </c>
       <c r="R18" t="n">
-        <v>7050112</v>
+        <v>7050036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,12 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468338</v>
+        <v>124468512</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2690,41 +2693,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461500</v>
+        <v>461530</v>
       </c>
       <c r="R19" t="n">
-        <v>7050112</v>
+        <v>7050097</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2753,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2763,12 +2766,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2783,22 +2786,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124469194</v>
+        <v>124468898</v>
       </c>
       <c r="B20" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2811,34 +2814,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461630</v>
+        <v>461593</v>
       </c>
       <c r="R20" t="n">
-        <v>7050036</v>
+        <v>7050052</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2870,7 +2873,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2880,12 +2883,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,19 +2903,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468401</v>
+        <v>124468413</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2948,14 +2951,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461503</v>
+        <v>461514</v>
       </c>
       <c r="R21" t="n">
-        <v>7050083</v>
+        <v>7050104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2987,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2997,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,22 +3020,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124469127</v>
+        <v>124468367</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,43 +3048,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461609</v>
+        <v>461494</v>
       </c>
       <c r="R22" t="n">
-        <v>7050050</v>
+        <v>7050108</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3113,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3123,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,22 +3137,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468954</v>
+        <v>124468401</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3171,37 +3165,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461595</v>
+        <v>461503</v>
       </c>
       <c r="R23" t="n">
-        <v>7050056</v>
+        <v>7050083</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3233,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3243,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3257,29 +3248,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124469282</v>
+        <v>124468629</v>
       </c>
       <c r="B24" t="n">
-        <v>77743</v>
+        <v>91363</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3288,38 +3278,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461663</v>
+        <v>461548</v>
       </c>
       <c r="R24" t="n">
-        <v>7050034</v>
+        <v>7050059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3351,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3361,7 +3354,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3370,74 +3368,92 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124468629</v>
+        <v>124294849</v>
       </c>
       <c r="B25" t="n">
-        <v>91363</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461548</v>
+        <v>461329</v>
       </c>
       <c r="R25" t="n">
-        <v>7050059</v>
+        <v>7050171</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3461,27 +3477,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ringhack på gammal tall i gammal tallskog nära sjöstrand</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3490,24 +3506,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468954</v>
+        <v>124468902</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461595</v>
+        <v>461582</v>
       </c>
       <c r="R4" t="n">
-        <v>7050056</v>
+        <v>7050071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1008,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124469282</v>
+        <v>124468413</v>
       </c>
       <c r="B5" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461663</v>
+        <v>461514</v>
       </c>
       <c r="R5" t="n">
-        <v>7050034</v>
+        <v>7050104</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468605</v>
+        <v>124468318</v>
       </c>
       <c r="B6" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461539</v>
+        <v>461483</v>
       </c>
       <c r="R6" t="n">
-        <v>7050084</v>
+        <v>7050111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468946</v>
+        <v>124469127</v>
       </c>
       <c r="B7" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1276,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461594</v>
+        <v>461609</v>
       </c>
       <c r="R7" t="n">
-        <v>7050052</v>
+        <v>7050050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124469540</v>
+        <v>124468367</v>
       </c>
       <c r="B8" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,34 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461502</v>
+        <v>461494</v>
       </c>
       <c r="R8" t="n">
-        <v>7050054</v>
+        <v>7050108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468176</v>
+        <v>124468866</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,34 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461418</v>
+        <v>461582</v>
       </c>
       <c r="R9" t="n">
-        <v>7050112</v>
+        <v>7050058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468263</v>
+        <v>124468954</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1636,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461459</v>
+        <v>461595</v>
       </c>
       <c r="R10" t="n">
-        <v>7050134</v>
+        <v>7050056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,12 +1708,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,6 +1722,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1727,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468318</v>
+        <v>124468338</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,34 +1757,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461483</v>
+        <v>461500</v>
       </c>
       <c r="R11" t="n">
-        <v>7050111</v>
+        <v>7050112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1826,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,22 +1846,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468687</v>
+        <v>124468898</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,34 +1874,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461555</v>
+        <v>461593</v>
       </c>
       <c r="R12" t="n">
-        <v>7050078</v>
+        <v>7050052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,12 +1943,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,22 +1963,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469127</v>
+        <v>124469194</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,43 +1991,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461609</v>
+        <v>461630</v>
       </c>
       <c r="R13" t="n">
-        <v>7050050</v>
+        <v>7050036</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,12 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,22 +2080,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124469219</v>
+        <v>124468263</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,43 +2108,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461680</v>
+        <v>461459</v>
       </c>
       <c r="R14" t="n">
-        <v>7049995</v>
+        <v>7050134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,12 +2177,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,22 +2197,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468866</v>
+        <v>124468605</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,34 +2225,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461582</v>
+        <v>461539</v>
       </c>
       <c r="R15" t="n">
-        <v>7050058</v>
+        <v>7050084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,12 +2294,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,22 +2314,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468338</v>
+        <v>124469219</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,34 +2342,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461500</v>
+        <v>461680</v>
       </c>
       <c r="R16" t="n">
-        <v>7050112</v>
+        <v>7049995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,12 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,10 +2452,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468902</v>
+        <v>124468687</v>
       </c>
       <c r="B17" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,21 +2468,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461582</v>
+        <v>461555</v>
       </c>
       <c r="R17" t="n">
-        <v>7050071</v>
+        <v>7050078</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2537,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124469194</v>
+        <v>124468401</v>
       </c>
       <c r="B18" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2585,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461630</v>
+        <v>461503</v>
       </c>
       <c r="R18" t="n">
-        <v>7050036</v>
+        <v>7050083</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2644,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,12 +2654,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,12 +2674,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2798,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468898</v>
+        <v>124468176</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,34 +2819,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461593</v>
+        <v>461418</v>
       </c>
       <c r="R20" t="n">
-        <v>7050052</v>
+        <v>7050112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2878,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,12 +2888,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,22 +2908,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468413</v>
+        <v>124468946</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,34 +2936,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461514</v>
+        <v>461594</v>
       </c>
       <c r="R21" t="n">
-        <v>7050104</v>
+        <v>7050052</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,12 +3005,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,22 +3025,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468367</v>
+        <v>124469282</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,21 +3053,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461494</v>
+        <v>461663</v>
       </c>
       <c r="R22" t="n">
-        <v>7050108</v>
+        <v>7050034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3122,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468401</v>
+        <v>124469540</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461503</v>
+        <v>461502</v>
       </c>
       <c r="R23" t="n">
-        <v>7050083</v>
+        <v>7050054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468902</v>
+        <v>124468866</v>
       </c>
       <c r="B4" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>461582</v>
       </c>
       <c r="R4" t="n">
-        <v>7050071</v>
+        <v>7050058</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +1014,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468413</v>
+        <v>124468401</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1062,14 +1062,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461514</v>
+        <v>461503</v>
       </c>
       <c r="R5" t="n">
-        <v>7050104</v>
+        <v>7050083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468318</v>
+        <v>124468263</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461483</v>
+        <v>461459</v>
       </c>
       <c r="R6" t="n">
-        <v>7050111</v>
+        <v>7050134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124469127</v>
+        <v>124468898</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,43 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461609</v>
+        <v>461593</v>
       </c>
       <c r="R7" t="n">
-        <v>7050050</v>
+        <v>7050052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468367</v>
+        <v>124468512</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,41 +1389,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461494</v>
+        <v>461530</v>
       </c>
       <c r="R8" t="n">
-        <v>7050108</v>
+        <v>7050097</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468866</v>
+        <v>124468318</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1539,14 +1530,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461582</v>
+        <v>461483</v>
       </c>
       <c r="R9" t="n">
-        <v>7050058</v>
+        <v>7050111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1599,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468954</v>
+        <v>124469282</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,37 +1627,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461595</v>
+        <v>461663</v>
       </c>
       <c r="R10" t="n">
-        <v>7050056</v>
+        <v>7050034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,12 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1705,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1741,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468338</v>
+        <v>124468687</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,34 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461500</v>
+        <v>461555</v>
       </c>
       <c r="R11" t="n">
-        <v>7050112</v>
+        <v>7050078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,12 +1808,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,22 +1828,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468898</v>
+        <v>124468605</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,34 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461593</v>
+        <v>461539</v>
       </c>
       <c r="R12" t="n">
-        <v>7050052</v>
+        <v>7050084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,12 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,12 +1945,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2092,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468263</v>
+        <v>124468954</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,34 +2090,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461459</v>
+        <v>461595</v>
       </c>
       <c r="R14" t="n">
-        <v>7050134</v>
+        <v>7050056</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,12 +2162,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,6 +2176,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468605</v>
+        <v>124468413</v>
       </c>
       <c r="B15" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2249,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461539</v>
+        <v>461514</v>
       </c>
       <c r="R15" t="n">
-        <v>7050084</v>
+        <v>7050104</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2280,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124469219</v>
+        <v>124468338</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,43 +2328,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461680</v>
+        <v>461500</v>
       </c>
       <c r="R16" t="n">
-        <v>7049995</v>
+        <v>7050112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,12 +2397,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468687</v>
+        <v>124468946</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,34 +2445,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461555</v>
+        <v>461594</v>
       </c>
       <c r="R17" t="n">
-        <v>7050078</v>
+        <v>7050052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,12 +2514,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2557,22 +2534,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468401</v>
+        <v>124468367</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2585,34 +2562,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461503</v>
+        <v>461494</v>
       </c>
       <c r="R18" t="n">
-        <v>7050083</v>
+        <v>7050108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,12 +2631,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,22 +2651,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468512</v>
+        <v>124468176</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,41 +2675,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461530</v>
+        <v>461418</v>
       </c>
       <c r="R19" t="n">
-        <v>7050097</v>
+        <v>7050112</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2771,12 +2748,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468176</v>
+        <v>124468902</v>
       </c>
       <c r="B20" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2819,21 +2796,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2820,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461418</v>
+        <v>461582</v>
       </c>
       <c r="R20" t="n">
-        <v>7050112</v>
+        <v>7050071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2888,12 +2865,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2920,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468946</v>
+        <v>124469540</v>
       </c>
       <c r="B21" t="n">
-        <v>88359</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2936,21 +2913,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461594</v>
+        <v>461502</v>
       </c>
       <c r="R21" t="n">
-        <v>7050052</v>
+        <v>7050054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2995,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,12 +2982,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124469282</v>
+        <v>124469127</v>
       </c>
       <c r="B22" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,34 +3030,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461663</v>
+        <v>461609</v>
       </c>
       <c r="R22" t="n">
-        <v>7050034</v>
+        <v>7050050</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +3098,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,7 +3108,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,22 +3128,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124469540</v>
+        <v>124469219</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,34 +3156,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461502</v>
+        <v>461680</v>
       </c>
       <c r="R23" t="n">
-        <v>7050054</v>
+        <v>7049995</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124295214</v>
+        <v>124295359</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461495</v>
+        <v>461531</v>
       </c>
       <c r="R2" t="n">
-        <v>7050108</v>
+        <v>7050055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124295359</v>
+        <v>124295214</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461531</v>
+        <v>461495</v>
       </c>
       <c r="R3" t="n">
-        <v>7050055</v>
+        <v>7050108</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468866</v>
+        <v>124468413</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -945,14 +945,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461582</v>
+        <v>461514</v>
       </c>
       <c r="R4" t="n">
-        <v>7050058</v>
+        <v>7050104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +1014,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468401</v>
+        <v>124469219</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1059,17 +1059,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461503</v>
+        <v>461680</v>
       </c>
       <c r="R5" t="n">
-        <v>7050083</v>
+        <v>7049995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468263</v>
+        <v>124468866</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461459</v>
+        <v>461582</v>
       </c>
       <c r="R6" t="n">
-        <v>7050134</v>
+        <v>7050058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468898</v>
+        <v>124469194</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1285,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461593</v>
+        <v>461630</v>
       </c>
       <c r="R7" t="n">
-        <v>7050052</v>
+        <v>7050036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,12 +1374,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1494,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468318</v>
+        <v>124468367</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1519,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461483</v>
+        <v>461494</v>
       </c>
       <c r="R9" t="n">
-        <v>7050111</v>
+        <v>7050108</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1840,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468605</v>
+        <v>124468401</v>
       </c>
       <c r="B12" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,34 +1865,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461539</v>
+        <v>461503</v>
       </c>
       <c r="R12" t="n">
-        <v>7050084</v>
+        <v>7050083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,12 +1934,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,22 +1954,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469194</v>
+        <v>124468263</v>
       </c>
       <c r="B13" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,21 +1982,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1997,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461630</v>
+        <v>461459</v>
       </c>
       <c r="R13" t="n">
-        <v>7050036</v>
+        <v>7050134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,12 +2051,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468954</v>
+        <v>124468318</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,37 +2099,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461595</v>
+        <v>461483</v>
       </c>
       <c r="R14" t="n">
-        <v>7050056</v>
+        <v>7050111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2162,12 +2168,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2182,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2195,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468413</v>
+        <v>124468898</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,34 +2216,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461514</v>
+        <v>461593</v>
       </c>
       <c r="R15" t="n">
-        <v>7050104</v>
+        <v>7050052</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2275,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2285,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,22 +2305,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468338</v>
+        <v>124468946</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461500</v>
+        <v>461594</v>
       </c>
       <c r="R16" t="n">
-        <v>7050112</v>
+        <v>7050052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,12 +2402,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468946</v>
+        <v>124469127</v>
       </c>
       <c r="B17" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,34 +2450,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461594</v>
+        <v>461609</v>
       </c>
       <c r="R17" t="n">
-        <v>7050052</v>
+        <v>7050050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,7 +2518,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,12 +2528,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,14 +2553,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468367</v>
+        <v>124468338</v>
       </c>
       <c r="B18" t="n">
         <v>74901</v>
@@ -2582,14 +2596,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461494</v>
+        <v>461500</v>
       </c>
       <c r="R18" t="n">
-        <v>7050108</v>
+        <v>7050112</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2635,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,12 +2645,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,22 +2665,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468176</v>
+        <v>124469540</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,34 +2693,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461418</v>
+        <v>461502</v>
       </c>
       <c r="R19" t="n">
-        <v>7050112</v>
+        <v>7050054</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2752,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,12 +2762,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,22 +2782,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468902</v>
+        <v>124468954</v>
       </c>
       <c r="B20" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,34 +2810,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461582</v>
+        <v>461595</v>
       </c>
       <c r="R20" t="n">
-        <v>7050071</v>
+        <v>7050056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,7 +2872,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,12 +2882,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,6 +2896,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2897,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124469540</v>
+        <v>124468902</v>
       </c>
       <c r="B21" t="n">
         <v>77743</v>
@@ -2933,14 +2951,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461502</v>
+        <v>461582</v>
       </c>
       <c r="R21" t="n">
-        <v>7050054</v>
+        <v>7050071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,22 +3020,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124469127</v>
+        <v>124468605</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,43 +3048,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461609</v>
+        <v>461539</v>
       </c>
       <c r="R22" t="n">
-        <v>7050050</v>
+        <v>7050084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3098,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3108,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,22 +3137,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124469219</v>
+        <v>124468176</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,43 +3165,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461680</v>
+        <v>461418</v>
       </c>
       <c r="R23" t="n">
-        <v>7049995</v>
+        <v>7050112</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468413</v>
+        <v>124468898</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461514</v>
+        <v>461593</v>
       </c>
       <c r="R4" t="n">
-        <v>7050104</v>
+        <v>7050052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +1014,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124469219</v>
+        <v>124469127</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461680</v>
+        <v>461609</v>
       </c>
       <c r="R5" t="n">
-        <v>7049995</v>
+        <v>7050050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468866</v>
+        <v>124468413</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1188,14 +1188,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461582</v>
+        <v>461514</v>
       </c>
       <c r="R6" t="n">
-        <v>7050058</v>
+        <v>7050104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124469194</v>
+        <v>124468367</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,21 +1285,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461630</v>
+        <v>461494</v>
       </c>
       <c r="R7" t="n">
-        <v>7050036</v>
+        <v>7050108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468512</v>
+        <v>124468946</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>88359</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,41 +1398,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461530</v>
+        <v>461594</v>
       </c>
       <c r="R8" t="n">
-        <v>7050097</v>
+        <v>7050052</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468367</v>
+        <v>124468318</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461494</v>
+        <v>461483</v>
       </c>
       <c r="R9" t="n">
-        <v>7050108</v>
+        <v>7050111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,7 +1620,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124469282</v>
+        <v>124469540</v>
       </c>
       <c r="B10" t="n">
         <v>77743</v>
@@ -1656,14 +1656,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461663</v>
+        <v>461502</v>
       </c>
       <c r="R10" t="n">
-        <v>7050034</v>
+        <v>7050054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,22 +1725,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468687</v>
+        <v>124468176</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,21 +1753,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1772,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461555</v>
+        <v>461418</v>
       </c>
       <c r="R11" t="n">
-        <v>7050078</v>
+        <v>7050112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,12 +1822,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468401</v>
+        <v>124468338</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,21 +1870,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461503</v>
+        <v>461500</v>
       </c>
       <c r="R12" t="n">
-        <v>7050083</v>
+        <v>7050112</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,12 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,17 +1964,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468263</v>
+        <v>124469219</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,34 +1987,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461459</v>
+        <v>461680</v>
       </c>
       <c r="R13" t="n">
-        <v>7050134</v>
+        <v>7049995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2055,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,12 +2065,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,22 +2085,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468318</v>
+        <v>124468954</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,34 +2113,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461483</v>
+        <v>461595</v>
       </c>
       <c r="R14" t="n">
-        <v>7050111</v>
+        <v>7050056</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,12 +2185,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,6 +2199,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2200,10 +2218,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468898</v>
+        <v>124468512</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,41 +2230,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461593</v>
+        <v>461530</v>
       </c>
       <c r="R15" t="n">
-        <v>7050052</v>
+        <v>7050097</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2285,12 +2303,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,22 +2323,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468946</v>
+        <v>124469282</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>77743</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2333,34 +2351,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461594</v>
+        <v>461663</v>
       </c>
       <c r="R16" t="n">
-        <v>7050052</v>
+        <v>7050034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2392,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,12 +2420,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,19 +2435,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124469127</v>
+        <v>124468401</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2467,26 +2480,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461609</v>
+        <v>461503</v>
       </c>
       <c r="R17" t="n">
-        <v>7050050</v>
+        <v>7050083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2528,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,17 +2557,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468338</v>
+        <v>124468605</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,34 +2580,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461500</v>
+        <v>461539</v>
       </c>
       <c r="R18" t="n">
-        <v>7050112</v>
+        <v>7050084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2635,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2645,12 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2665,22 +2669,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124469540</v>
+        <v>124468263</v>
       </c>
       <c r="B19" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2693,34 +2697,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461502</v>
+        <v>461459</v>
       </c>
       <c r="R19" t="n">
-        <v>7050054</v>
+        <v>7050134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2752,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2762,12 +2766,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,22 +2786,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468954</v>
+        <v>124469194</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,37 +2814,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461595</v>
+        <v>461630</v>
       </c>
       <c r="R20" t="n">
-        <v>7050056</v>
+        <v>7050036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2887,7 +2888,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2896,7 +2897,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468605</v>
+        <v>124468866</v>
       </c>
       <c r="B22" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,34 +3048,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461539</v>
+        <v>461582</v>
       </c>
       <c r="R22" t="n">
-        <v>7050084</v>
+        <v>7050058</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,22 +3137,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468176</v>
+        <v>124468687</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461418</v>
+        <v>461555</v>
       </c>
       <c r="R23" t="n">
-        <v>7050112</v>
+        <v>7050078</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124295359</v>
+        <v>124295214</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461531</v>
+        <v>461495</v>
       </c>
       <c r="R2" t="n">
-        <v>7050055</v>
+        <v>7050108</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124295214</v>
+        <v>124295359</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461495</v>
+        <v>461531</v>
       </c>
       <c r="R3" t="n">
-        <v>7050108</v>
+        <v>7050055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468898</v>
+        <v>124469127</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461593</v>
+        <v>461609</v>
       </c>
       <c r="R4" t="n">
-        <v>7050052</v>
+        <v>7050050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,17 +1028,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124469127</v>
+        <v>124468898</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,43 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461609</v>
+        <v>461593</v>
       </c>
       <c r="R5" t="n">
-        <v>7050050</v>
+        <v>7050052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468401</v>
+        <v>124468605</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,34 +2463,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461503</v>
+        <v>461539</v>
       </c>
       <c r="R17" t="n">
-        <v>7050083</v>
+        <v>7050084</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,22 +2552,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468605</v>
+        <v>124468401</v>
       </c>
       <c r="B18" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2580,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461539</v>
+        <v>461503</v>
       </c>
       <c r="R18" t="n">
-        <v>7050084</v>
+        <v>7050083</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,12 +2669,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468902</v>
+        <v>124468866</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>461582</v>
       </c>
       <c r="R21" t="n">
-        <v>7050071</v>
+        <v>7050058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,22 +3020,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468866</v>
+        <v>124468902</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,34 +3048,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>461582</v>
       </c>
       <c r="R22" t="n">
-        <v>7050058</v>
+        <v>7050071</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,12 +3137,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -2447,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468605</v>
+        <v>124468401</v>
       </c>
       <c r="B17" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,34 +2463,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461539</v>
+        <v>461503</v>
       </c>
       <c r="R17" t="n">
-        <v>7050084</v>
+        <v>7050083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,22 +2552,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468401</v>
+        <v>124468605</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2580,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461503</v>
+        <v>461539</v>
       </c>
       <c r="R18" t="n">
-        <v>7050083</v>
+        <v>7050084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,12 +2669,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468866</v>
+        <v>124468902</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>461582</v>
       </c>
       <c r="R21" t="n">
-        <v>7050058</v>
+        <v>7050071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,22 +3020,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468902</v>
+        <v>124468866</v>
       </c>
       <c r="B22" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,34 +3048,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>461582</v>
       </c>
       <c r="R22" t="n">
-        <v>7050071</v>
+        <v>7050058</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,12 +3137,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468413</v>
+        <v>124468687</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461514</v>
+        <v>461555</v>
       </c>
       <c r="R6" t="n">
-        <v>7050104</v>
+        <v>7050078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468367</v>
+        <v>124469540</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1285,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461494</v>
+        <v>461502</v>
       </c>
       <c r="R7" t="n">
-        <v>7050108</v>
+        <v>7050054</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1374,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468946</v>
+        <v>124468176</v>
       </c>
       <c r="B8" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,34 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461594</v>
+        <v>461418</v>
       </c>
       <c r="R8" t="n">
-        <v>7050052</v>
+        <v>7050112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468318</v>
+        <v>124468946</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461483</v>
+        <v>461594</v>
       </c>
       <c r="R9" t="n">
-        <v>7050111</v>
+        <v>7050052</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124469540</v>
+        <v>124468413</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,34 +1636,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461502</v>
+        <v>461514</v>
       </c>
       <c r="R10" t="n">
-        <v>7050054</v>
+        <v>7050104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,22 +1725,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468176</v>
+        <v>124468401</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,34 +1753,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461418</v>
+        <v>461503</v>
       </c>
       <c r="R11" t="n">
-        <v>7050112</v>
+        <v>7050083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,22 +1842,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468338</v>
+        <v>124468512</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,41 +1866,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461500</v>
+        <v>461530</v>
       </c>
       <c r="R12" t="n">
-        <v>7050112</v>
+        <v>7050097</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,22 +1959,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469219</v>
+        <v>124468954</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,43 +1987,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461680</v>
+        <v>461595</v>
       </c>
       <c r="R13" t="n">
-        <v>7049995</v>
+        <v>7050056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2065,12 +2059,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,28 +2073,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468954</v>
+        <v>124468605</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,37 +2108,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461595</v>
+        <v>461539</v>
       </c>
       <c r="R14" t="n">
-        <v>7050056</v>
+        <v>7050084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2175,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,12 +2177,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,7 +2191,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2218,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468512</v>
+        <v>124469282</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,41 +2221,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461530</v>
+        <v>461663</v>
       </c>
       <c r="R15" t="n">
-        <v>7050097</v>
+        <v>7050034</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2293,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,12 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 sjungande</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2335,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124469282</v>
+        <v>124468367</v>
       </c>
       <c r="B16" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2375,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461663</v>
+        <v>461494</v>
       </c>
       <c r="R16" t="n">
-        <v>7050034</v>
+        <v>7050108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,7 +2406,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468401</v>
+        <v>124468902</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,34 +2454,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461503</v>
+        <v>461582</v>
       </c>
       <c r="R17" t="n">
-        <v>7050083</v>
+        <v>7050071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2513,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2523,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,22 +2543,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468605</v>
+        <v>124468866</v>
       </c>
       <c r="B18" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2571,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461539</v>
+        <v>461582</v>
       </c>
       <c r="R18" t="n">
-        <v>7050084</v>
+        <v>7050058</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2630,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,12 +2640,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,22 +2660,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468263</v>
+        <v>124468318</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2688,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461459</v>
+        <v>461483</v>
       </c>
       <c r="R19" t="n">
-        <v>7050134</v>
+        <v>7050111</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,12 +2757,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,10 +2789,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124469194</v>
+        <v>124468338</v>
       </c>
       <c r="B20" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,34 +2805,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461630</v>
+        <v>461500</v>
       </c>
       <c r="R20" t="n">
-        <v>7050036</v>
+        <v>7050112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2864,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,12 +2874,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,22 +2894,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468902</v>
+        <v>124468263</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,21 +2922,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461582</v>
+        <v>461459</v>
       </c>
       <c r="R21" t="n">
-        <v>7050071</v>
+        <v>7050134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,7 +2991,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3032,7 +3023,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468866</v>
+        <v>124469219</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3065,17 +3056,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461582</v>
+        <v>461680</v>
       </c>
       <c r="R22" t="n">
-        <v>7050058</v>
+        <v>7049995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3142,17 +3142,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468687</v>
+        <v>124469194</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461555</v>
+        <v>461630</v>
       </c>
       <c r="R23" t="n">
-        <v>7050078</v>
+        <v>7050036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124469127</v>
+        <v>124468687</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -942,26 +942,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461609</v>
+        <v>461555</v>
       </c>
       <c r="R4" t="n">
-        <v>7050050</v>
+        <v>7050078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468898</v>
+        <v>124468401</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461593</v>
+        <v>461503</v>
       </c>
       <c r="R5" t="n">
-        <v>7050052</v>
+        <v>7050083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,14 +1136,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468687</v>
+        <v>124468413</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1192,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461555</v>
+        <v>461514</v>
       </c>
       <c r="R6" t="n">
-        <v>7050078</v>
+        <v>7050104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124469540</v>
+        <v>124468318</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461502</v>
+        <v>461483</v>
       </c>
       <c r="R7" t="n">
-        <v>7050054</v>
+        <v>7050111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468176</v>
+        <v>124468605</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461418</v>
+        <v>461539</v>
       </c>
       <c r="R8" t="n">
-        <v>7050112</v>
+        <v>7050084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468946</v>
+        <v>124469194</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>77743</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461594</v>
+        <v>461630</v>
       </c>
       <c r="R9" t="n">
-        <v>7050052</v>
+        <v>7050036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1584,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1599,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468413</v>
+        <v>124468902</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1660,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461514</v>
+        <v>461582</v>
       </c>
       <c r="R10" t="n">
-        <v>7050104</v>
+        <v>7050071</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,12 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468401</v>
+        <v>124468866</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1777,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461503</v>
+        <v>461582</v>
       </c>
       <c r="R11" t="n">
-        <v>7050083</v>
+        <v>7050058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,12 +1813,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,17 +1838,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468512</v>
+        <v>124468946</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,41 +1857,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461530</v>
+        <v>461594</v>
       </c>
       <c r="R12" t="n">
-        <v>7050097</v>
+        <v>7050052</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,22 +1950,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468954</v>
+        <v>124469219</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,37 +1978,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461595</v>
+        <v>461680</v>
       </c>
       <c r="R13" t="n">
-        <v>7050056</v>
+        <v>7049995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,12 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,29 +2070,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468605</v>
+        <v>124469127</v>
       </c>
       <c r="B14" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,34 +2104,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461539</v>
+        <v>461609</v>
       </c>
       <c r="R14" t="n">
-        <v>7050084</v>
+        <v>7050050</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2172,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,12 +2182,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,22 +2202,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124469282</v>
+        <v>124468338</v>
       </c>
       <c r="B15" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,34 +2230,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461663</v>
+        <v>461500</v>
       </c>
       <c r="R15" t="n">
-        <v>7050034</v>
+        <v>7050112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2289,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2299,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,22 +2319,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468367</v>
+        <v>124469540</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,34 +2347,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461494</v>
+        <v>461502</v>
       </c>
       <c r="R16" t="n">
-        <v>7050108</v>
+        <v>7050054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,12 +2416,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,22 +2436,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468902</v>
+        <v>124468954</v>
       </c>
       <c r="B17" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,34 +2464,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461582</v>
+        <v>461595</v>
       </c>
       <c r="R17" t="n">
-        <v>7050071</v>
+        <v>7050056</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2523,12 +2536,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,6 +2550,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2555,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468866</v>
+        <v>124468898</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,21 +2585,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2595,10 +2609,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461582</v>
+        <v>461593</v>
       </c>
       <c r="R18" t="n">
-        <v>7050058</v>
+        <v>7050052</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,7 +2644,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2640,12 +2654,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2672,10 +2686,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468318</v>
+        <v>124468512</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,41 +2698,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461483</v>
+        <v>461530</v>
       </c>
       <c r="R19" t="n">
-        <v>7050111</v>
+        <v>7050097</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2747,7 +2761,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2757,12 +2771,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2789,10 +2803,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468338</v>
+        <v>124469282</v>
       </c>
       <c r="B20" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2805,34 +2819,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461500</v>
+        <v>461663</v>
       </c>
       <c r="R20" t="n">
-        <v>7050112</v>
+        <v>7050034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2864,7 +2878,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2874,12 +2888,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,19 +2903,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468263</v>
+        <v>124468367</v>
       </c>
       <c r="B21" t="n">
         <v>74901</v>
@@ -2946,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461459</v>
+        <v>461494</v>
       </c>
       <c r="R21" t="n">
-        <v>7050134</v>
+        <v>7050108</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2981,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2991,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124469219</v>
+        <v>124468176</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,43 +3048,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461680</v>
+        <v>461418</v>
       </c>
       <c r="R22" t="n">
-        <v>7049995</v>
+        <v>7050112</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,22 +3137,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124469194</v>
+        <v>124468263</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461630</v>
+        <v>461459</v>
       </c>
       <c r="R23" t="n">
-        <v>7050036</v>
+        <v>7050134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468687</v>
+        <v>124469194</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461555</v>
+        <v>461630</v>
       </c>
       <c r="R4" t="n">
-        <v>7050078</v>
+        <v>7050036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468401</v>
+        <v>124468176</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461503</v>
+        <v>461418</v>
       </c>
       <c r="R5" t="n">
-        <v>7050083</v>
+        <v>7050112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,19 +1131,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468413</v>
+        <v>124468401</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1179,14 +1179,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461514</v>
+        <v>461503</v>
       </c>
       <c r="R6" t="n">
-        <v>7050104</v>
+        <v>7050083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468318</v>
+        <v>124468605</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461483</v>
+        <v>461539</v>
       </c>
       <c r="R7" t="n">
-        <v>7050111</v>
+        <v>7050084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468605</v>
+        <v>124468902</v>
       </c>
       <c r="B8" t="n">
         <v>77743</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461539</v>
+        <v>461582</v>
       </c>
       <c r="R8" t="n">
-        <v>7050084</v>
+        <v>7050071</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124469194</v>
+        <v>124468338</v>
       </c>
       <c r="B9" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461630</v>
+        <v>461500</v>
       </c>
       <c r="R9" t="n">
-        <v>7050036</v>
+        <v>7050112</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,22 +1599,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468902</v>
+        <v>124469219</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,34 +1627,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461582</v>
+        <v>461680</v>
       </c>
       <c r="R10" t="n">
-        <v>7050071</v>
+        <v>7049995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,22 +1725,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468866</v>
+        <v>124468367</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,34 +1753,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461582</v>
+        <v>461494</v>
       </c>
       <c r="R11" t="n">
-        <v>7050058</v>
+        <v>7050108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,12 +1822,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,22 +1842,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468946</v>
+        <v>124468954</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,34 +1870,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461594</v>
+        <v>461595</v>
       </c>
       <c r="R12" t="n">
-        <v>7050052</v>
+        <v>7050056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1947,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,28 +1956,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124469219</v>
+        <v>124468512</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,50 +1987,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461680</v>
+        <v>461530</v>
       </c>
       <c r="R13" t="n">
-        <v>7049995</v>
+        <v>7050097</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2046,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2060,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,22 +2080,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124469127</v>
+        <v>124469282</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,43 +2108,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461609</v>
+        <v>461663</v>
       </c>
       <c r="R14" t="n">
-        <v>7050050</v>
+        <v>7050034</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2172,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2182,12 +2177,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,22 +2192,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468338</v>
+        <v>124468866</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,21 +2220,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2254,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461500</v>
+        <v>461582</v>
       </c>
       <c r="R15" t="n">
-        <v>7050112</v>
+        <v>7050058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2279,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,12 +2289,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124469540</v>
+        <v>124469127</v>
       </c>
       <c r="B16" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,34 +2337,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461502</v>
+        <v>461609</v>
       </c>
       <c r="R16" t="n">
-        <v>7050054</v>
+        <v>7050050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2416,12 +2415,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,7 +2447,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468954</v>
+        <v>124468898</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2482,19 +2481,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461595</v>
+        <v>461593</v>
       </c>
       <c r="R17" t="n">
-        <v>7050056</v>
+        <v>7050052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2526,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2536,12 +2532,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2550,29 +2546,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468898</v>
+        <v>124468946</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2585,21 +2580,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2609,7 +2604,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461593</v>
+        <v>461594</v>
       </c>
       <c r="R18" t="n">
         <v>7050052</v>
@@ -2644,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,12 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,17 +2674,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468512</v>
+        <v>124468318</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,41 +2693,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461530</v>
+        <v>461483</v>
       </c>
       <c r="R19" t="n">
-        <v>7050097</v>
+        <v>7050111</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2771,12 +2766,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,10 +2798,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124469282</v>
+        <v>124468687</v>
       </c>
       <c r="B20" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2819,21 +2814,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2843,10 +2838,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461663</v>
+        <v>461555</v>
       </c>
       <c r="R20" t="n">
-        <v>7050034</v>
+        <v>7050078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,7 +2873,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2888,7 +2883,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468367</v>
+        <v>124468263</v>
       </c>
       <c r="B21" t="n">
         <v>74901</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461494</v>
+        <v>461459</v>
       </c>
       <c r="R21" t="n">
-        <v>7050108</v>
+        <v>7050134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468176</v>
+        <v>124468413</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,21 +3048,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461418</v>
+        <v>461514</v>
       </c>
       <c r="R22" t="n">
-        <v>7050112</v>
+        <v>7050104</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468263</v>
+        <v>124469540</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,34 +3165,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461459</v>
+        <v>461502</v>
       </c>
       <c r="R23" t="n">
-        <v>7050134</v>
+        <v>7050054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124469194</v>
+        <v>124468367</v>
       </c>
       <c r="B4" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461630</v>
+        <v>461494</v>
       </c>
       <c r="R4" t="n">
-        <v>7050036</v>
+        <v>7050108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468176</v>
+        <v>124468898</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461418</v>
+        <v>461593</v>
       </c>
       <c r="R5" t="n">
-        <v>7050112</v>
+        <v>7050052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,19 +1131,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468401</v>
+        <v>124468866</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461503</v>
+        <v>461582</v>
       </c>
       <c r="R6" t="n">
-        <v>7050083</v>
+        <v>7050058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468605</v>
+        <v>124468338</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461539</v>
+        <v>461500</v>
       </c>
       <c r="R7" t="n">
-        <v>7050084</v>
+        <v>7050112</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468902</v>
+        <v>124468687</v>
       </c>
       <c r="B8" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461582</v>
+        <v>461555</v>
       </c>
       <c r="R8" t="n">
-        <v>7050071</v>
+        <v>7050078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468338</v>
+        <v>124468401</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461500</v>
+        <v>461503</v>
       </c>
       <c r="R9" t="n">
-        <v>7050112</v>
+        <v>7050083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124469219</v>
+        <v>124468902</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,43 +1627,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461680</v>
+        <v>461582</v>
       </c>
       <c r="R10" t="n">
-        <v>7049995</v>
+        <v>7050071</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,12 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,22 +1716,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124468367</v>
+        <v>124469282</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1777,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461494</v>
+        <v>461663</v>
       </c>
       <c r="R11" t="n">
-        <v>7050108</v>
+        <v>7050034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,12 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124468954</v>
+        <v>124469127</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,37 +1856,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461595</v>
+        <v>461609</v>
       </c>
       <c r="R12" t="n">
-        <v>7050056</v>
+        <v>7050050</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,12 +1934,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,29 +1948,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468512</v>
+        <v>124468318</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,41 +1978,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461530</v>
+        <v>461483</v>
       </c>
       <c r="R13" t="n">
-        <v>7050097</v>
+        <v>7050111</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,12 +2051,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124469282</v>
+        <v>124468954</v>
       </c>
       <c r="B14" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,34 +2099,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461663</v>
+        <v>461595</v>
       </c>
       <c r="R14" t="n">
-        <v>7050034</v>
+        <v>7050056</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,7 +2171,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,6 +2185,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124468866</v>
+        <v>124469194</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,34 +2220,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461582</v>
+        <v>461630</v>
       </c>
       <c r="R15" t="n">
-        <v>7050058</v>
+        <v>7050036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,22 +2309,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124469127</v>
+        <v>124468605</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,43 +2337,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461609</v>
+        <v>461539</v>
       </c>
       <c r="R16" t="n">
-        <v>7050050</v>
+        <v>7050084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,12 +2406,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,22 +2426,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468898</v>
+        <v>124468176</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,34 +2454,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461593</v>
+        <v>461418</v>
       </c>
       <c r="R17" t="n">
-        <v>7050052</v>
+        <v>7050112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2513,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,12 +2523,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,22 +2543,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124468946</v>
+        <v>124469219</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2571,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461594</v>
+        <v>461680</v>
       </c>
       <c r="R18" t="n">
-        <v>7050052</v>
+        <v>7049995</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468318</v>
+        <v>124468946</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,34 +2697,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461483</v>
+        <v>461594</v>
       </c>
       <c r="R19" t="n">
-        <v>7050111</v>
+        <v>7050052</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,19 +2786,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468687</v>
+        <v>124468413</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461555</v>
+        <v>461514</v>
       </c>
       <c r="R20" t="n">
-        <v>7050078</v>
+        <v>7050104</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124468263</v>
+        <v>124469540</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461459</v>
+        <v>461502</v>
       </c>
       <c r="R21" t="n">
-        <v>7050134</v>
+        <v>7050054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,22 +3020,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468413</v>
+        <v>124468512</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,41 +3044,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461514</v>
+        <v>461530</v>
       </c>
       <c r="R22" t="n">
-        <v>7050104</v>
+        <v>7050097</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124469540</v>
+        <v>124468263</v>
       </c>
       <c r="B23" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,34 +3165,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461502</v>
+        <v>461459</v>
       </c>
       <c r="R23" t="n">
-        <v>7050054</v>
+        <v>7050134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124468367</v>
+        <v>124469127</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461494</v>
+        <v>461609</v>
       </c>
       <c r="R4" t="n">
-        <v>7050108</v>
+        <v>7050050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124468898</v>
+        <v>124468946</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1051,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,7 +1075,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461593</v>
+        <v>461594</v>
       </c>
       <c r="R5" t="n">
         <v>7050052</v>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal barrblandskog</t>
+          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124468866</v>
+        <v>124468898</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461582</v>
+        <v>461593</v>
       </c>
       <c r="R6" t="n">
-        <v>7050058</v>
+        <v>7050052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124468338</v>
+        <v>124468401</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1285,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461500</v>
+        <v>461503</v>
       </c>
       <c r="R7" t="n">
-        <v>7050112</v>
+        <v>7050083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124468687</v>
+        <v>124468512</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,41 +1398,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461555</v>
+        <v>461530</v>
       </c>
       <c r="R8" t="n">
-        <v>7050078</v>
+        <v>7050097</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
+          <t>1 sjungande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124468401</v>
+        <v>124468176</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461503</v>
+        <v>461418</v>
       </c>
       <c r="R9" t="n">
-        <v>7050083</v>
+        <v>7050112</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 bål 50 cm lång på gammal död gran i gammal barrblandskog</t>
+          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124468902</v>
+        <v>124468687</v>
       </c>
       <c r="B10" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461582</v>
+        <v>461555</v>
       </c>
       <c r="R10" t="n">
-        <v>7050071</v>
+        <v>7050078</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>Ett 20-tal bålar på 5 granar i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124469282</v>
+        <v>124468413</v>
       </c>
       <c r="B11" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1753,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461663</v>
+        <v>461514</v>
       </c>
       <c r="R11" t="n">
-        <v>7050034</v>
+        <v>7050104</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1822,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett 10-tal bålar på en gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124469127</v>
+        <v>124468902</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,43 +1870,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461609</v>
+        <v>461582</v>
       </c>
       <c r="R12" t="n">
-        <v>7050050</v>
+        <v>7050071</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,12 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,22 +1959,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124468318</v>
+        <v>124468367</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,21 +1987,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461483</v>
+        <v>461494</v>
       </c>
       <c r="R13" t="n">
-        <v>7050111</v>
+        <v>7050108</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,12 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124468954</v>
+        <v>124468338</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,37 +2104,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461595</v>
+        <v>461500</v>
       </c>
       <c r="R14" t="n">
-        <v>7050056</v>
+        <v>7050112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2173,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,29 +2187,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124469194</v>
+        <v>124469219</v>
       </c>
       <c r="B15" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,34 +2221,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461630</v>
+        <v>461680</v>
       </c>
       <c r="R15" t="n">
-        <v>7050036</v>
+        <v>7049995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,7 +2289,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,12 +2299,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran ca 25 cm i diameter</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,19 +2319,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124468605</v>
+        <v>124469194</v>
       </c>
       <c r="B16" t="n">
         <v>77743</v>
@@ -2361,10 +2371,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461539</v>
+        <v>461630</v>
       </c>
       <c r="R16" t="n">
-        <v>7050084</v>
+        <v>7050036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,12 +2416,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>På gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124468176</v>
+        <v>124468954</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,34 +2464,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461418</v>
+        <v>461595</v>
       </c>
       <c r="R17" t="n">
-        <v>7050112</v>
+        <v>7050056</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2523,12 +2536,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran ca 45 cm i diameter I äldre barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,6 +2550,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2555,7 +2569,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124469219</v>
+        <v>124468318</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2588,26 +2602,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461680</v>
+        <v>461483</v>
       </c>
       <c r="R18" t="n">
-        <v>7049995</v>
+        <v>7050111</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,7 +2644,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,12 +2654,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>5 bålar på en gran 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,22 +2674,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124468946</v>
+        <v>124468263</v>
       </c>
       <c r="B19" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,34 +2702,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461594</v>
+        <v>461459</v>
       </c>
       <c r="R19" t="n">
-        <v>7050052</v>
+        <v>7050134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2761,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,12 +2771,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På toppbruten gammal granlåga i gammal barrblandskog</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,22 +2791,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124468413</v>
+        <v>124469540</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,34 +2819,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrudden, Bergmyrudden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461514</v>
+        <v>461502</v>
       </c>
       <c r="R20" t="n">
-        <v>7050104</v>
+        <v>7050054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2878,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,12 +2888,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett 10-tal bålar på en gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,22 +2908,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124469540</v>
+        <v>124468866</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,21 +2936,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461502</v>
+        <v>461582</v>
       </c>
       <c r="R21" t="n">
-        <v>7050054</v>
+        <v>7050058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,12 +3005,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3032,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124468512</v>
+        <v>124468605</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,41 +3049,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fiskodlingen, Landön, Offerdal, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461530</v>
+        <v>461539</v>
       </c>
       <c r="R22" t="n">
-        <v>7050097</v>
+        <v>7050084</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3107,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,12 +3122,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 sjungande</t>
+          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3149,10 +3154,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124468263</v>
+        <v>124469282</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,21 +3170,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461459</v>
+        <v>461663</v>
       </c>
       <c r="R23" t="n">
-        <v>7050134</v>
+        <v>7050034</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3229,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3239,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gran ca 35 cm i diameter i äldre barrblandskog</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -3405,7 +3405,7 @@
         <v>124294849</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 10991-2025 artfynd.xlsx
+++ b/artfynd/A 10991-2025 artfynd.xlsx
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
